--- a/Cleaned-Data.xlsx
+++ b/Cleaned-Data.xlsx
@@ -77,17 +77,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2383,7 +2379,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4685,7 +4681,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -10963,7 +10959,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -12263,7 +12259,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -20521,7 +20517,7 @@
     <col width="37" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -20813,7 +20809,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>SKU-C-1002</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -20919,7 +20919,7 @@
         <v>49.99</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -20937,7 +20937,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>SKU-U-1003</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="n"/>
     </row>
     <row r="7">
@@ -21036,7 +21040,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>604.555.0190</t>
+          <t>604-555-0190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -21069,7 +21073,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>SKU-C-1004</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -21185,7 +21193,7 @@
         <v>26.5</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n">
@@ -21403,7 +21411,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O13" s="3" t="n"/>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1007</t>
+        </is>
+      </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -21438,7 +21450,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>647.555.0130</t>
+          <t>647-555-0130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -21675,7 +21687,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O17" s="3" t="n"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1009</t>
+        </is>
+      </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -21891,12 +21907,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Urban Sources</t>
+          <t>Urban Source</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>512.555.0173</t>
+          <t>512-555-0173</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -21997,7 +22013,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O22" s="2" t="n"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>SKU-U-1013</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
           <t>duplicate desc?</t>
@@ -22032,7 +22052,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>416.555.0144</t>
+          <t>416-555-0144</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -22100,7 +22120,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>(404)555-0181</t>
+          <t>404-555-0181</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -22329,7 +22349,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O27" s="3" t="n"/>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1017</t>
+        </is>
+      </c>
       <c r="P27" s="3" t="n"/>
     </row>
     <row r="28">
@@ -22694,7 +22718,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>604.555.0190</t>
+          <t>604-555-0190</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -22727,7 +22751,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O33" s="3" t="n"/>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>SKU-C-1004</t>
+        </is>
+      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
           <t>legacy/vendor code</t>
@@ -22789,7 +22817,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O34" s="2" t="n"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>SKU-C-1010</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="n"/>
     </row>
     <row r="35">
@@ -22853,7 +22885,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O35" s="3" t="n"/>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>SKU-C-1002</t>
+        </is>
+      </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
           <t>seasonal color</t>
@@ -22917,7 +22953,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O36" s="2" t="n"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>SKU-U-1017</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -22985,7 +23025,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O37" s="3" t="n"/>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1007</t>
+        </is>
+      </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
           <t>seasonal color</t>
@@ -23020,7 +23064,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>(404)555-0181</t>
+          <t>404-555-0181</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -23053,7 +23097,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O38" s="2" t="n"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>SKU-U-1015</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
           <t>seasonal color</t>
@@ -23119,7 +23167,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O39" s="3" t="n"/>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1005</t>
+        </is>
+      </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -23183,7 +23235,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>SKU-C-1012</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -23251,7 +23307,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O41" s="3" t="n"/>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1007</t>
+        </is>
+      </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
           <t>duplicate desc?</t>
@@ -23319,7 +23379,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O42" s="2" t="n"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>SKU-C-1004</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
           <t>legacy/vendor code</t>
@@ -23383,7 +23447,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O43" s="3" t="n"/>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1017</t>
+        </is>
+      </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
           <t>duplicate desc?</t>
@@ -23451,7 +23519,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O44" s="2" t="n"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>SKU-C-1016</t>
+        </is>
+      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -23558,7 +23630,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>416.555.0144</t>
+          <t>416-555-0144</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -23591,7 +23663,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O46" s="2" t="n"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>SKU-C-1014</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
           <t>legacy/vendor code</t>
@@ -23621,7 +23697,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Urban Sources</t>
+          <t>Urban Source</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -23657,7 +23733,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O47" s="3" t="n"/>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1005</t>
+        </is>
+      </c>
       <c r="P47" s="3" t="n"/>
     </row>
     <row r="48">
@@ -23721,7 +23801,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O48" s="2" t="n"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>SKU-U-1007</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
           <t>seasonal color</t>
@@ -23789,7 +23873,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="O49" s="3" t="n"/>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1013</t>
+        </is>
+      </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
           <t>duplicate desc?</t>
@@ -23927,7 +24015,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O51" s="3" t="n"/>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1005</t>
+        </is>
+      </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -23958,7 +24050,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>(404)555-0181</t>
+          <t>404-555-0181</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -23991,7 +24083,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O52" s="2" t="n"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>SKU-U-1017</t>
+        </is>
+      </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -24022,7 +24118,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>(404)555-0181</t>
+          <t>404-555-0181</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -24055,7 +24151,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O53" s="3" t="n"/>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1017</t>
+        </is>
+      </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
           <t>vendor note mismatch</t>
@@ -24117,7 +24217,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O54" s="2" t="n"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>SKU-U-1019</t>
+        </is>
+      </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
           <t>legacy/vendor code</t>
@@ -24251,7 +24355,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O56" s="2" t="n"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>SKU-U-1005</t>
+        </is>
+      </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
           <t>seasonal color</t>
@@ -24313,7 +24421,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O57" s="3" t="n"/>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>SKU-C-1010</t>
+        </is>
+      </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
           <t>duplicate desc?</t>
@@ -24453,7 +24565,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O59" s="3" t="n"/>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>SKU-C-1002</t>
+        </is>
+      </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
           <t>legacy/vendor code</t>
@@ -24488,7 +24604,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>(404)555-0181</t>
+          <t>404-555-0181</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -24551,7 +24667,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Urban Sources</t>
+          <t>Urban Source</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -24589,7 +24705,11 @@
           <t>N</t>
         </is>
       </c>
-      <c r="O61" s="3" t="n"/>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>SKU-U-1007</t>
+        </is>
+      </c>
       <c r="P61" s="3" t="n"/>
     </row>
   </sheetData>
@@ -24603,7 +24723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -24611,20 +24731,35 @@
     <col width="72" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>SKU casing inconsistent (sku-c-1002 vs SKU-C-1002)</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Normalized all SKUs to UPPERCASE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Issue Identified</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Resolution Applied</t>
         </is>
       </c>
     </row>
@@ -24644,6 +24779,9 @@
           <t>Parsed with dayfirst disambiguation; standardized to ISO YYYY-MM-DD</t>
         </is>
       </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -24661,6 +24799,9 @@
           <t>Normalized to US/CA; 3 nulls inferred from order_id prefix (CORD=CA, UORD=US) — 100% consistent across all 200 rows</t>
         </is>
       </c>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -24678,6 +24819,9 @@
           <t>Normalized: title-cased; MC → Mastercard</t>
         </is>
       </c>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -24695,6 +24839,9 @@
           <t>All converted to decimal rate (0.10, 0.05); text labels like "promo5" parsed by extracting numeric portion</t>
         </is>
       </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -24712,6 +24859,9 @@
           <t>All converted to decimal rate; 33 rows legitimately null. 12 additional rows filled deterministically (unique rate confirmed within same order_id)</t>
         </is>
       </c>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -24729,6 +24879,9 @@
           <t>Stripped prefixes; stored as numeric. line_total left null where missing — does not reconcile to a simple formula, preserved as-is</t>
         </is>
       </c>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -24746,6 +24899,9 @@
           <t>Extracted numeric portion via regex; stored as integer</t>
         </is>
       </c>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -24763,6 +24919,9 @@
           <t>Split into customer_name and customer_type (Student / Loyalty / Guest / Standard)</t>
         </is>
       </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -24780,6 +24939,9 @@
           <t>Extracted primary category before delimiter; normalized to 7 canonical categories</t>
         </is>
       </c>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -24797,6 +24959,9 @@
           <t>Re-derived from source: weight units → grams; length units (in, ") → cm. "one size" preserved as text</t>
         </is>
       </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -24814,6 +24979,9 @@
           <t>Normalized to title case using Product_Supplier_Master as canonical reference per SKU</t>
         </is>
       </c>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -24831,6 +24999,9 @@
           <t>Fixed to: emma_wilson@school.edu, ella.wright@example.ca</t>
         </is>
       </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -24848,6 +25019,9 @@
           <t>Filled using exact match on (customer_name + customer_type + ship_country) key — only where that key mapped to exactly one unique email in the data</t>
         </is>
       </c>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -24865,6 +25039,9 @@
           <t>Mapped all to 7 canonical categories</t>
         </is>
       </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -24882,6 +25059,9 @@
           <t>Stripped currency prefixes; stored as numeric</t>
         </is>
       </c>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -24899,6 +25079,9 @@
           <t>All converted to grams; column renamed weight_g</t>
         </is>
       </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -24916,6 +25099,9 @@
           <t>All converted to cm; column renamed length_cm</t>
         </is>
       </c>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -24933,6 +25119,9 @@
           <t>Removed exact duplicate rows; variant rows with same SKU but different descriptions retained (parent_sku field tracks relationship)</t>
         </is>
       </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -24950,6 +25139,9 @@
           <t>Replaced with "1 each" for consistency</t>
         </is>
       </c>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -24967,6 +25159,9 @@
           <t>Filled using exact match on SKU — only where all other rows with same SKU had identical values</t>
         </is>
       </c>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -24982,6 +25177,149 @@
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Fixed using exact case-insensitive match between ALL CAPS original and product table; affected SKUs: SKU-U-1015, SKU-U-1019, SKU-C-1008, SKU-C-1012, SKU-C-1018</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sales_Dump</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>return_flag: 40 rows were null</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Filled with "N" (not returned). Assumption: absence of a return flag indicates no return was recorded. All 40 null rows had no return-related notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sales_Dump</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>LN-019 (CORD-1010): sale_date parsed as 2025-09-10 from "09-10-2025"</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Corrected to 2025-10-09. CORD prefix = Canadian order; DD-MM-YYYY convention confirmed by matching order line LN-059 (same order_id, "October 9 2025" = unambiguous Oct 9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Product_Supplier_Master</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>reorder_level: 4 rows had value "ten" (text); 2 rows (ClickStorm Gaming Mouse Mini, TrailSip Bottle) were incorrectly filled with sibling-row value instead of being normalized to 10</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Fixed ClickStorm Gaming Mouse Mini and TrailSip Bottle reorder_level to 10. Other "ten" rows (EchoWave Headphones, EchoWave Headphones Student Edition) correctly normalized to 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Product_Supplier_Master</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>parent_sku: 41 obvious variant rows (Mini, Student Edition, color/size variants) had null parent_sku</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Filled parent_sku = sku for all variant rows. Consistent with pattern in original source where parent_sku always equals sku (all variants share SKU with their parent product).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Product_Supplier_Master</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>vendor_phone: mixed formats — XXX-XXX-XXXX, XXX.XXX.XXXX, (XXX)XXX-XXXX</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Normalized all vendor phone numbers to XXX-XXX-XXXX format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Product_Supplier_Master</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>vendor_name: "Urban Sources" (typo) vs "Urban Source" — same phone number, clearly same vendor</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>"Urban Sources" → "Urban Source" (2 rows). Majority form (14:2) and logical correctness confirm the correct name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sales_Dump</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>3 additional CORD (Canadian) order dates misparse: LN-042 (09-11-2025), LN-105 (08/10/2025), LN-118 (04-11-2025) — ambiguous MM-DD defaulted to US format</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Corrected to DD-MM-YYYY (Canadian convention): LN-042 → 2025-11-09, LN-105 → 2025-10-08, LN-118 → 2025-11-04. All CORD orders cross-checked; no other ambiguous dates affected.</t>
         </is>
       </c>
     </row>
@@ -24996,7 +25334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -25007,3325 +25345,3369 @@
     <col width="35" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="n"/>
-      <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="n"/>
-      <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 5</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Filled cells</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>weight_g</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>size_or_weight</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Cell</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Filled Value</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Key Used</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>H17</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>emma.wilson@example.ca</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Emma Wilson | Standard | CA</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>H32</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>H49</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>H59</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>zoe_garcia@school.edu</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Zoe Garcia | Guest | US</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>H90</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>zoe_garcia@school.edu</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Zoe Garcia | Guest | US</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>H116</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>H118</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>H120</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>H121</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>H127</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>zoe_garcia@school.edu</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Zoe Garcia | Standard | US</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>H129</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>lucastaylor@gmail.com</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Lucas Taylor | Guest | US</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>H137</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>mason_rivera@school.edu</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Mason Rivera | Loyalty | CA</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>H138</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>mason_rivera@school.edu</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Mason Rivera | Loyalty | CA</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>H140</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>mason_rivera@school.edu</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Mason Rivera | Loyalty | CA</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>H142</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>mason_rivera@school.edu</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Mason Rivera | Loyalty | CA</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>H144</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>mason_rivera@school.edu</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Mason Rivera | Loyalty | CA</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>H152</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>emmawilson@gmail.com</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Emma Wilson | Loyalty | US</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>H157</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>H159</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>H161</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>H163</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>maya_chen@school.edu</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Maya Chen | Student | US</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>H174</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>chloemartin@gmail.com</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Chloe Martin | Student | CA</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>H196</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>ethan_lee@school.edu</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Ethan Lee | Standard | US</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>H198</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>ethan_lee@school.edu</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Exact match on customer_name + customer_type + ship_country</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>Ethan Lee | Standard | US</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D38" s="2" t="n">
         <v>0.0825</v>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>UORD-1041</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>P24</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.0825</v>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>UORD-1049</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>P59</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D40" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>UORD-1016</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>P74</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D41" s="3" t="n">
         <v>0.0825</v>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>UORD-1022</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>P78</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D42" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>UORD-1032</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>P79</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="D43" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>UORD-1019</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>P92</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n">
+      <c r="D44" s="2" t="n">
         <v>0.0825</v>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>UORD-1048</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>P138</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>CORD-1074</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>P140</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n">
+      <c r="D46" s="2" t="n">
         <v>0.13</v>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>CORD-1074</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>P148</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.0825</v>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>UORD-1084</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>P184</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n">
+      <c r="D48" s="2" t="n">
         <v>0.0825</v>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>UORD-1100</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>P193</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D49" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Unique non-null tax_rate already present on another line in the same order_id</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>UORD-1109</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>T81</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>size_or_weight</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>one size</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null size_or_weight elsewhere in Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1001</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>T171</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>size_or_weight</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>one size</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null size_or_weight elsewhere in Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1001</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>T195</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>size_or_weight</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>one size</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null size_or_weight elsewhere in Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1001</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>B2</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>LEG-U-1001</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1001</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>LEG-C-1002</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1002</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>B9</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>LEG-U-1005</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1005</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>B10</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>LEG-C-1006</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1006</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>B13</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>LEG-U-1007</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1007</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>B17</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>LEG-U-1009</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1009</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>B19</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>LEG-U-1011</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1011</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>B22</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>LEG-U-1013</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1013</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>B23</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>LEG-C-1014</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1014</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>B25</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>LEG-C-1016</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1016</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>B31</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>LEG-C-1020</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1020</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>B33</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>LEG-C-1004</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1004</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>B35</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>LEG-C-1002</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1002</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>B37</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>LEG-U-1007</t>
         </is>
       </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F66" s="5" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1007</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>B38</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>LEG-U-1015</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1015</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>B40</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>LEG-C-1012</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1012</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>B45</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>LEG-C-1018</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F69" s="5" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1018</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>B48</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>LEG-U-1007</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F70" s="5" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1007</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>B49</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>LEG-U-1013</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1013</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>B51</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>LEG-U-1005</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1005</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>B56</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>LEG-U-1005</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1005</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>B58</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>LEG-C-1020</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1020</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>B59</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>LEG-C-1002</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1002</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>B60</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>LEG-U-1011</t>
         </is>
       </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F76" s="5" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1011</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>J3</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="D77" s="5" t="n">
+      <c r="D77" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1002</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>J6</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="D78" s="5" t="n">
+      <c r="D78" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1003</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>J7</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D79" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1004</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>J10</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="D80" s="5" t="n">
+      <c r="D80" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1006</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>J28</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="D81" s="5" t="n">
+      <c r="D81" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1018</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>J31</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="D82" s="5" t="n">
+      <c r="D82" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1020</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>J42</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="D83" s="5" t="n">
+      <c r="D83" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F83" s="5" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1004</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>J45</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="D84" s="5" t="n">
+      <c r="D84" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F84" s="5" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1018</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>K4</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>3-pack</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1002</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>K7</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Case of 6</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1004</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>K12</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>3-pack</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1007</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>K29</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>1 each</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1018</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>K35</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>3-pack</t>
         </is>
       </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1002</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>K37</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>3-pack</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1007</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>K42</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Case of 6</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1004</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>K59</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>3-pack</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1002</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>K61</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>3-pack</t>
         </is>
       </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1007</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>L5</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>weight_g</t>
         </is>
       </c>
-      <c r="D94" s="5" t="n">
+      <c r="D94" s="2" t="n">
         <v>498.95</v>
       </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1003</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>L15</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>weight_g</t>
         </is>
       </c>
-      <c r="D95" s="5" t="n">
+      <c r="D95" s="3" t="n">
         <v>340</v>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1008</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>L16</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>weight_g</t>
         </is>
       </c>
-      <c r="D96" s="5" t="n">
+      <c r="D96" s="2" t="n">
         <v>340.19</v>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1009</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="D97" s="5" t="n">
+      <c r="D97" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F97" s="5" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>SKU-C-1004</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="D98" s="5" t="n">
+      <c r="D98" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1006</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="D99" s="5" t="n">
+      <c r="D99" s="3" t="n">
         <v>25.91</v>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1007</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>M21</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="D100" s="5" t="n">
+      <c r="D100" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>SKU-U-1013</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>M41</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="D101" s="5" t="n">
+      <c r="D101" s="3" t="n">
         <v>25.91</v>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1007</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>M42</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="D102" s="5" t="n">
+      <c r="D102" s="2" t="n">
         <v>25.4</v>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>SKU-C-1004</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>M48</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="D103" s="5" t="n">
+      <c r="D103" s="3" t="n">
         <v>25.91</v>
       </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>Exact same SKU has one consistent non-null value elsewhere in Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>SKU-U-1007</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n"/>
-      <c r="B104" s="5" t="n"/>
-      <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
-      <c r="E104" s="5" t="n"/>
-      <c r="F104" s="5" t="n"/>
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n"/>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="5" t="n"/>
-      <c r="D105" s="5" t="n"/>
-      <c r="E105" s="5" t="n"/>
-      <c r="F105" s="5" t="n"/>
+      <c r="A105" s="3" t="n"/>
+      <c r="B105" s="3" t="n"/>
+      <c r="C105" s="3" t="n"/>
+      <c r="D105" s="3" t="n"/>
+      <c r="E105" s="3" t="n"/>
+      <c r="F105" s="3" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Missing before</t>
         </is>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Missing after</t>
         </is>
       </c>
-      <c r="E106" s="5" t="n"/>
-      <c r="F106" s="5" t="n"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>customer_email</t>
         </is>
       </c>
-      <c r="C107" s="5" t="n">
+      <c r="C107" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D107" s="5" t="n">
+      <c r="D107" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="E107" s="5" t="n"/>
-      <c r="F107" s="5" t="n"/>
+      <c r="E107" s="3" t="n"/>
+      <c r="F107" s="3" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>tax_rate</t>
         </is>
       </c>
-      <c r="C108" s="5" t="n">
+      <c r="C108" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D108" s="5" t="n">
+      <c r="D108" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="E108" s="5" t="n"/>
-      <c r="F108" s="5" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>line_total</t>
         </is>
       </c>
-      <c r="C109" s="5" t="n">
+      <c r="C109" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="D109" s="5" t="n">
+      <c r="D109" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="E109" s="5" t="n"/>
-      <c r="F109" s="5" t="n"/>
+      <c r="E109" s="3" t="n"/>
+      <c r="F109" s="3" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B110" s="5" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>size_or_weight</t>
         </is>
       </c>
-      <c r="C110" s="5" t="n">
+      <c r="C110" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D110" s="5" t="n">
+      <c r="D110" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E110" s="5" t="n"/>
-      <c r="F110" s="5" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>Sales_Dump_Cleaned</t>
         </is>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="C111" s="5" t="n">
+      <c r="C111" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="D111" s="5" t="n">
+      <c r="D111" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="E111" s="5" t="n"/>
-      <c r="F111" s="5" t="n"/>
+      <c r="E111" s="3" t="n"/>
+      <c r="F111" s="3" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>alt_sku</t>
         </is>
       </c>
-      <c r="C112" s="5" t="n">
+      <c r="C112" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D112" s="5" t="n">
+      <c r="D112" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E112" s="5" t="n"/>
-      <c r="F112" s="5" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>reorder_level</t>
         </is>
       </c>
-      <c r="C113" s="5" t="n">
+      <c r="C113" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D113" s="5" t="n">
+      <c r="D113" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E113" s="5" t="n"/>
-      <c r="F113" s="5" t="n"/>
+      <c r="E113" s="3" t="n"/>
+      <c r="F113" s="3" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>pack_size</t>
         </is>
       </c>
-      <c r="C114" s="5" t="n">
+      <c r="C114" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D114" s="5" t="n">
+      <c r="D114" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E114" s="5" t="n"/>
-      <c r="F114" s="5" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>weight_g</t>
         </is>
       </c>
-      <c r="C115" s="5" t="n">
+      <c r="C115" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="D115" s="5" t="n">
+      <c r="D115" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E115" s="5" t="n"/>
-      <c r="F115" s="5" t="n"/>
+      <c r="E115" s="3" t="n"/>
+      <c r="F115" s="3" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="C116" s="5" t="n">
+      <c r="C116" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D116" s="5" t="n">
+      <c r="D116" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E116" s="5" t="n"/>
-      <c r="F116" s="5" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>parent_sku</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n">
+      <c r="C117" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="D117" s="5" t="n">
+      <c r="D117" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="E117" s="5" t="n"/>
-      <c r="F117" s="5" t="n"/>
+      <c r="E117" s="3" t="n"/>
+      <c r="F117" s="3" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Product_Supplier_Cleaned</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="C118" s="5" t="n">
+      <c r="C118" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D118" s="5" t="n">
+      <c r="D118" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E118" s="5" t="n"/>
-      <c r="F118" s="5" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTION NOTE</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>reorder_level fill count was logged as 8</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Only 4 were null→filled. The other 4 were text→numeric normalization ("ten"→10), not null fills. Additionally, 2 of those text normalization rows were incorrectly converted (ClickStorm Gaming Mouse Mini and TrailSip Bottle) and have been corrected to 10.</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n"/>
+      <c r="E119" s="3" t="n"/>
+      <c r="F119" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
